--- a/UTF-8FORMATO REEMBOLSO DE TRANSPORTE V4 ultimo 12 mayo.xlsx
+++ b/UTF-8FORMATO REEMBOLSO DE TRANSPORTE V4 ultimo 12 mayo.xlsx
@@ -1,23 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tania.rojas\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jeronimo Zapata\Documents\GitHub\adminlogisticauv\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{336EFDA1-E46F-4C02-95E4-2FA14993B5B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F68B281C-4449-4A64-ABDE-7D2D11AD253F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Formato Reembolso" sheetId="1" r:id="rId1"/>
     <sheet name="Control de Cambios" sheetId="2" state="hidden" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Formato Reembolso'!$A$8:$M$71</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Formato Reembolso'!$A$2:$M$71</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
@@ -389,7 +389,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t>Los campos adicionados no tienen explicación para quien lo diligencia?
 Si bien la DGI sabe como diligenciar si otra persona quiere conocer a que se refieren estos campos deberian tener ayuda de texto</t>
@@ -399,7 +399,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">
 </t>
@@ -640,7 +640,7 @@
     <numFmt numFmtId="164" formatCode="_(&quot;$&quot;\ * #,##0.00_);_(&quot;$&quot;\ * \(#,##0.00\);_(&quot;$&quot;\ * &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="165" formatCode="_ &quot;$&quot;\ * #,##0_ ;_ &quot;$&quot;\ * \-#,##0_ ;_ &quot;$&quot;\ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="20" x14ac:knownFonts="1">
+  <fonts count="18" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -746,19 +746,6 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="Tahoma"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="Tahoma"/>
-      <charset val="1"/>
-    </font>
   </fonts>
   <fills count="6">
     <fill>
@@ -1443,6 +1430,123 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="10" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="11" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="12" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="10" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="11" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="12" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="17" fillId="0" borderId="10" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="17" fillId="0" borderId="11" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="17" fillId="0" borderId="12" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="16" fillId="5" borderId="10" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="16" fillId="5" borderId="11" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="16" fillId="5" borderId="12" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1460,6 +1564,291 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="43" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1470,21 +1859,6 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="17" fillId="0" borderId="10" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="17" fillId="0" borderId="11" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="17" fillId="0" borderId="12" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1503,357 +1877,6 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="43" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="5" borderId="10" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="5" borderId="11" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="5" borderId="12" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="5" borderId="10" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="5" borderId="11" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="5" borderId="12" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="16" fillId="5" borderId="10" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="16" fillId="5" borderId="11" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="16" fillId="5" borderId="12" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="3" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1866,45 +1889,9 @@
     <xf numFmtId="14" fontId="11" fillId="3" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="4">
-    <cellStyle name="Moneda" xfId="2" builtinId="4"/>
+    <cellStyle name="Currency" xfId="2" builtinId="4"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
     <cellStyle name="Normal 3" xfId="3" xr:uid="{00000000-0005-0000-0000-000003000000}"/>
@@ -2262,172 +2249,172 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:M71"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11.453125" defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="1.7109375" customWidth="1"/>
-    <col min="2" max="2" width="21.140625" style="2" customWidth="1"/>
-    <col min="3" max="3" width="11.7109375" customWidth="1"/>
-    <col min="4" max="4" width="18.7109375" customWidth="1"/>
-    <col min="5" max="5" width="2.7109375" customWidth="1"/>
-    <col min="6" max="6" width="20.7109375" customWidth="1"/>
-    <col min="7" max="7" width="11.140625" customWidth="1"/>
-    <col min="8" max="8" width="15.28515625" customWidth="1"/>
-    <col min="9" max="9" width="13.7109375" customWidth="1"/>
-    <col min="10" max="12" width="7.7109375" customWidth="1"/>
-    <col min="13" max="13" width="3.42578125" customWidth="1"/>
+    <col min="1" max="1" width="1.7265625" customWidth="1"/>
+    <col min="2" max="2" width="21.1796875" style="2" customWidth="1"/>
+    <col min="3" max="3" width="11.7265625" customWidth="1"/>
+    <col min="4" max="4" width="18.7265625" customWidth="1"/>
+    <col min="5" max="5" width="2.7265625" customWidth="1"/>
+    <col min="6" max="6" width="20.7265625" customWidth="1"/>
+    <col min="7" max="7" width="11.1796875" customWidth="1"/>
+    <col min="8" max="8" width="15.26953125" customWidth="1"/>
+    <col min="9" max="9" width="13.7265625" customWidth="1"/>
+    <col min="10" max="12" width="7.7265625" customWidth="1"/>
+    <col min="13" max="13" width="3.453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="69"/>
-      <c r="B1" s="70"/>
-      <c r="C1" s="70"/>
-      <c r="D1" s="70"/>
-      <c r="E1" s="70"/>
-      <c r="F1" s="70"/>
-      <c r="G1" s="70"/>
-      <c r="H1" s="70"/>
-      <c r="I1" s="70"/>
-      <c r="J1" s="70"/>
-      <c r="K1" s="70"/>
-      <c r="L1" s="70"/>
-      <c r="M1" s="71"/>
-    </row>
-    <row r="2" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="72"/>
-      <c r="B2" s="75"/>
-      <c r="C2" s="76"/>
-      <c r="D2" s="128" t="s">
+    <row r="1" spans="1:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="47"/>
+      <c r="B1" s="48"/>
+      <c r="C1" s="48"/>
+      <c r="D1" s="48"/>
+      <c r="E1" s="48"/>
+      <c r="F1" s="48"/>
+      <c r="G1" s="48"/>
+      <c r="H1" s="48"/>
+      <c r="I1" s="48"/>
+      <c r="J1" s="48"/>
+      <c r="K1" s="48"/>
+      <c r="L1" s="48"/>
+      <c r="M1" s="49"/>
+    </row>
+    <row r="2" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="147"/>
+      <c r="B2" s="150"/>
+      <c r="C2" s="151"/>
+      <c r="D2" s="119" t="s">
         <v>0</v>
       </c>
-      <c r="E2" s="129"/>
-      <c r="F2" s="129"/>
-      <c r="G2" s="129"/>
-      <c r="H2" s="130"/>
-      <c r="I2" s="110" t="s">
+      <c r="E2" s="120"/>
+      <c r="F2" s="120"/>
+      <c r="G2" s="120"/>
+      <c r="H2" s="121"/>
+      <c r="I2" s="102" t="s">
         <v>1</v>
       </c>
-      <c r="J2" s="111"/>
-      <c r="K2" s="112"/>
-      <c r="L2" s="112"/>
-      <c r="M2" s="113"/>
-    </row>
-    <row r="3" spans="1:13" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="73"/>
-      <c r="B3" s="77"/>
-      <c r="C3" s="78"/>
-      <c r="D3" s="131"/>
-      <c r="E3" s="132"/>
-      <c r="F3" s="132"/>
-      <c r="G3" s="132"/>
-      <c r="H3" s="133"/>
-      <c r="I3" s="114"/>
-      <c r="J3" s="115"/>
-      <c r="K3" s="116"/>
-      <c r="L3" s="116"/>
-      <c r="M3" s="117"/>
-    </row>
-    <row r="4" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="73"/>
-      <c r="B4" s="77"/>
-      <c r="C4" s="78"/>
-      <c r="D4" s="134" t="s">
+      <c r="J2" s="103"/>
+      <c r="K2" s="104"/>
+      <c r="L2" s="104"/>
+      <c r="M2" s="105"/>
+    </row>
+    <row r="3" spans="1:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="148"/>
+      <c r="B3" s="152"/>
+      <c r="C3" s="153"/>
+      <c r="D3" s="122"/>
+      <c r="E3" s="123"/>
+      <c r="F3" s="123"/>
+      <c r="G3" s="123"/>
+      <c r="H3" s="124"/>
+      <c r="I3" s="106"/>
+      <c r="J3" s="107"/>
+      <c r="K3" s="108"/>
+      <c r="L3" s="108"/>
+      <c r="M3" s="109"/>
+    </row>
+    <row r="4" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="148"/>
+      <c r="B4" s="152"/>
+      <c r="C4" s="153"/>
+      <c r="D4" s="125" t="s">
         <v>2</v>
       </c>
-      <c r="E4" s="135"/>
-      <c r="F4" s="135"/>
-      <c r="G4" s="135"/>
-      <c r="H4" s="136"/>
-      <c r="I4" s="179" t="s">
+      <c r="E4" s="126"/>
+      <c r="F4" s="126"/>
+      <c r="G4" s="126"/>
+      <c r="H4" s="127"/>
+      <c r="I4" s="131" t="s">
         <v>64</v>
       </c>
-      <c r="J4" s="180"/>
-      <c r="K4" s="181"/>
-      <c r="L4" s="181"/>
-      <c r="M4" s="182"/>
-    </row>
-    <row r="5" spans="1:13" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="73"/>
-      <c r="B5" s="77"/>
-      <c r="C5" s="78"/>
-      <c r="D5" s="61"/>
-      <c r="E5" s="62"/>
-      <c r="F5" s="62"/>
-      <c r="G5" s="62"/>
-      <c r="H5" s="63"/>
-      <c r="I5" s="183"/>
-      <c r="J5" s="184"/>
-      <c r="K5" s="185"/>
-      <c r="L5" s="185"/>
-      <c r="M5" s="186"/>
-    </row>
-    <row r="6" spans="1:13" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="73"/>
-      <c r="B6" s="77"/>
-      <c r="C6" s="78"/>
-      <c r="D6" s="58" t="s">
+      <c r="J4" s="132"/>
+      <c r="K4" s="133"/>
+      <c r="L4" s="133"/>
+      <c r="M4" s="134"/>
+    </row>
+    <row r="5" spans="1:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="148"/>
+      <c r="B5" s="152"/>
+      <c r="C5" s="153"/>
+      <c r="D5" s="128"/>
+      <c r="E5" s="129"/>
+      <c r="F5" s="129"/>
+      <c r="G5" s="129"/>
+      <c r="H5" s="130"/>
+      <c r="I5" s="135"/>
+      <c r="J5" s="136"/>
+      <c r="K5" s="137"/>
+      <c r="L5" s="137"/>
+      <c r="M5" s="138"/>
+    </row>
+    <row r="6" spans="1:13" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="148"/>
+      <c r="B6" s="152"/>
+      <c r="C6" s="153"/>
+      <c r="D6" s="175" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="59"/>
-      <c r="F6" s="59"/>
-      <c r="G6" s="59"/>
-      <c r="H6" s="60"/>
-      <c r="I6" s="187" t="s">
+      <c r="E6" s="176"/>
+      <c r="F6" s="176"/>
+      <c r="G6" s="176"/>
+      <c r="H6" s="177"/>
+      <c r="I6" s="139" t="s">
         <v>65</v>
       </c>
-      <c r="J6" s="188"/>
-      <c r="K6" s="189"/>
-      <c r="L6" s="189"/>
-      <c r="M6" s="190"/>
-    </row>
-    <row r="7" spans="1:13" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="73"/>
-      <c r="B7" s="79"/>
-      <c r="C7" s="80"/>
-      <c r="D7" s="61"/>
-      <c r="E7" s="62"/>
-      <c r="F7" s="62"/>
-      <c r="G7" s="62"/>
-      <c r="H7" s="63"/>
-      <c r="I7" s="138" t="s">
+      <c r="J6" s="140"/>
+      <c r="K6" s="141"/>
+      <c r="L6" s="141"/>
+      <c r="M6" s="142"/>
+    </row>
+    <row r="7" spans="1:13" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="148"/>
+      <c r="B7" s="154"/>
+      <c r="C7" s="155"/>
+      <c r="D7" s="128"/>
+      <c r="E7" s="129"/>
+      <c r="F7" s="129"/>
+      <c r="G7" s="129"/>
+      <c r="H7" s="130"/>
+      <c r="I7" s="143" t="s">
         <v>4</v>
       </c>
-      <c r="J7" s="139"/>
-      <c r="K7" s="140"/>
-      <c r="L7" s="140"/>
-      <c r="M7" s="141"/>
-    </row>
-    <row r="8" spans="1:13" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="73"/>
-      <c r="B8" s="118"/>
-      <c r="C8" s="118"/>
-      <c r="D8" s="118"/>
-      <c r="E8" s="118"/>
-      <c r="F8" s="118"/>
-      <c r="G8" s="118"/>
-      <c r="H8" s="118"/>
-      <c r="I8" s="118"/>
-      <c r="J8" s="118"/>
-      <c r="K8" s="118"/>
-      <c r="L8" s="118"/>
-      <c r="M8" s="119"/>
-    </row>
-    <row r="9" spans="1:13" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="73"/>
-      <c r="B9" s="70"/>
-      <c r="C9" s="70"/>
-      <c r="D9" s="70"/>
-      <c r="E9" s="70"/>
-      <c r="F9" s="70"/>
-      <c r="G9" s="70"/>
-      <c r="H9" s="70"/>
-      <c r="I9" s="70"/>
-      <c r="J9" s="70"/>
-      <c r="K9" s="70"/>
-      <c r="L9" s="70"/>
-      <c r="M9" s="71"/>
-    </row>
-    <row r="10" spans="1:13" ht="7.35" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="73"/>
+      <c r="J7" s="144"/>
+      <c r="K7" s="145"/>
+      <c r="L7" s="145"/>
+      <c r="M7" s="146"/>
+    </row>
+    <row r="8" spans="1:13" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="148"/>
+      <c r="B8" s="110"/>
+      <c r="C8" s="110"/>
+      <c r="D8" s="110"/>
+      <c r="E8" s="110"/>
+      <c r="F8" s="110"/>
+      <c r="G8" s="110"/>
+      <c r="H8" s="110"/>
+      <c r="I8" s="110"/>
+      <c r="J8" s="110"/>
+      <c r="K8" s="110"/>
+      <c r="L8" s="110"/>
+      <c r="M8" s="111"/>
+    </row>
+    <row r="9" spans="1:13" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="148"/>
+      <c r="B9" s="48"/>
+      <c r="C9" s="48"/>
+      <c r="D9" s="48"/>
+      <c r="E9" s="48"/>
+      <c r="F9" s="48"/>
+      <c r="G9" s="48"/>
+      <c r="H9" s="48"/>
+      <c r="I9" s="48"/>
+      <c r="J9" s="48"/>
+      <c r="K9" s="48"/>
+      <c r="L9" s="48"/>
+      <c r="M9" s="49"/>
+    </row>
+    <row r="10" spans="1:13" ht="7.4" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="148"/>
       <c r="C10" s="31"/>
       <c r="D10" s="31"/>
       <c r="E10" s="31"/>
@@ -2440,341 +2427,341 @@
       <c r="L10" s="32"/>
       <c r="M10" s="1"/>
     </row>
-    <row r="11" spans="1:13" ht="29.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="73"/>
-      <c r="B11" s="122" t="s">
+    <row r="11" spans="1:13" ht="29.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="148"/>
+      <c r="B11" s="113" t="s">
         <v>5</v>
       </c>
-      <c r="C11" s="123"/>
-      <c r="D11" s="123"/>
-      <c r="E11" s="123"/>
-      <c r="F11" s="123"/>
-      <c r="G11" s="123"/>
-      <c r="H11" s="123"/>
-      <c r="I11" s="123"/>
-      <c r="J11" s="123"/>
-      <c r="K11" s="123"/>
-      <c r="L11" s="123"/>
-      <c r="M11" s="124"/>
-    </row>
-    <row r="12" spans="1:13" ht="8.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="73"/>
-      <c r="B12" s="126"/>
-      <c r="C12" s="126"/>
-      <c r="D12" s="126"/>
-      <c r="E12" s="126"/>
-      <c r="F12" s="126"/>
-      <c r="G12" s="126"/>
-      <c r="H12" s="126"/>
-      <c r="I12" s="126"/>
-      <c r="J12" s="126"/>
-      <c r="K12" s="126"/>
-      <c r="L12" s="126"/>
-      <c r="M12" s="127"/>
-    </row>
-    <row r="13" spans="1:13" ht="23.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="73"/>
+      <c r="C11" s="114"/>
+      <c r="D11" s="114"/>
+      <c r="E11" s="114"/>
+      <c r="F11" s="114"/>
+      <c r="G11" s="114"/>
+      <c r="H11" s="114"/>
+      <c r="I11" s="114"/>
+      <c r="J11" s="114"/>
+      <c r="K11" s="114"/>
+      <c r="L11" s="114"/>
+      <c r="M11" s="115"/>
+    </row>
+    <row r="12" spans="1:13" ht="8.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="148"/>
+      <c r="B12" s="117"/>
+      <c r="C12" s="117"/>
+      <c r="D12" s="117"/>
+      <c r="E12" s="117"/>
+      <c r="F12" s="117"/>
+      <c r="G12" s="117"/>
+      <c r="H12" s="117"/>
+      <c r="I12" s="117"/>
+      <c r="J12" s="117"/>
+      <c r="K12" s="117"/>
+      <c r="L12" s="117"/>
+      <c r="M12" s="118"/>
+    </row>
+    <row r="13" spans="1:13" ht="23.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="148"/>
       <c r="B13" s="24" t="s">
         <v>6</v>
       </c>
-      <c r="C13" s="66"/>
-      <c r="D13" s="67"/>
-      <c r="E13" s="67"/>
-      <c r="F13" s="68"/>
-      <c r="G13" s="125" t="s">
+      <c r="C13" s="62"/>
+      <c r="D13" s="63"/>
+      <c r="E13" s="63"/>
+      <c r="F13" s="64"/>
+      <c r="G13" s="116" t="s">
         <v>7</v>
       </c>
-      <c r="H13" s="125"/>
-      <c r="I13" s="66"/>
-      <c r="J13" s="67"/>
-      <c r="K13" s="68"/>
+      <c r="H13" s="116"/>
+      <c r="I13" s="62"/>
+      <c r="J13" s="63"/>
+      <c r="K13" s="64"/>
       <c r="L13" s="18"/>
       <c r="M13" s="1"/>
     </row>
-    <row r="14" spans="1:13" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="73"/>
-      <c r="B14" s="64"/>
-      <c r="C14" s="64"/>
-      <c r="D14" s="64"/>
-      <c r="E14" s="64"/>
-      <c r="F14" s="64"/>
+    <row r="14" spans="1:13" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="148"/>
+      <c r="B14" s="75"/>
+      <c r="C14" s="75"/>
+      <c r="D14" s="75"/>
+      <c r="E14" s="75"/>
+      <c r="F14" s="75"/>
       <c r="G14" s="18"/>
-      <c r="H14" s="101"/>
-      <c r="I14" s="101"/>
-      <c r="J14" s="101"/>
-      <c r="K14" s="101"/>
-      <c r="L14" s="101"/>
-      <c r="M14" s="102"/>
-    </row>
-    <row r="15" spans="1:13" ht="24.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="73"/>
+      <c r="H14" s="51"/>
+      <c r="I14" s="51"/>
+      <c r="J14" s="51"/>
+      <c r="K14" s="51"/>
+      <c r="L14" s="51"/>
+      <c r="M14" s="52"/>
+    </row>
+    <row r="15" spans="1:13" ht="24.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="148"/>
       <c r="B15" s="28" t="s">
         <v>8</v>
       </c>
-      <c r="C15" s="153"/>
-      <c r="D15" s="154"/>
-      <c r="E15" s="154"/>
-      <c r="F15" s="155"/>
+      <c r="C15" s="93"/>
+      <c r="D15" s="94"/>
+      <c r="E15" s="94"/>
+      <c r="F15" s="95"/>
       <c r="G15" s="10"/>
       <c r="H15" s="33" t="s">
         <v>54</v>
       </c>
-      <c r="I15" s="66"/>
-      <c r="J15" s="67"/>
-      <c r="K15" s="68"/>
+      <c r="I15" s="62"/>
+      <c r="J15" s="63"/>
+      <c r="K15" s="64"/>
       <c r="M15" s="1"/>
     </row>
-    <row r="16" spans="1:13" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="73"/>
-      <c r="B16" s="82"/>
-      <c r="C16" s="82"/>
-      <c r="D16" s="82"/>
-      <c r="E16" s="82"/>
-      <c r="F16" s="82"/>
-      <c r="G16" s="82"/>
-      <c r="H16" s="82"/>
-      <c r="I16" s="82"/>
-      <c r="J16" s="82"/>
-      <c r="K16" s="82"/>
-      <c r="L16" s="82"/>
-      <c r="M16" s="83"/>
-    </row>
-    <row r="17" spans="1:13" ht="31.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="73"/>
-      <c r="B17" s="137" t="s">
+    <row r="16" spans="1:13" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="148"/>
+      <c r="B16" s="54"/>
+      <c r="C16" s="54"/>
+      <c r="D16" s="54"/>
+      <c r="E16" s="54"/>
+      <c r="F16" s="54"/>
+      <c r="G16" s="54"/>
+      <c r="H16" s="54"/>
+      <c r="I16" s="54"/>
+      <c r="J16" s="54"/>
+      <c r="K16" s="54"/>
+      <c r="L16" s="54"/>
+      <c r="M16" s="55"/>
+    </row>
+    <row r="17" spans="1:13" ht="31.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="148"/>
+      <c r="B17" s="91" t="s">
         <v>63</v>
       </c>
-      <c r="C17" s="137"/>
-      <c r="D17" s="137"/>
-      <c r="E17" s="121"/>
-      <c r="F17" s="120" t="s">
+      <c r="C17" s="91"/>
+      <c r="D17" s="91"/>
+      <c r="E17" s="92"/>
+      <c r="F17" s="112" t="s">
         <v>9</v>
       </c>
-      <c r="G17" s="121"/>
-      <c r="H17" s="120" t="s">
+      <c r="G17" s="92"/>
+      <c r="H17" s="112" t="s">
         <v>10</v>
       </c>
-      <c r="I17" s="137"/>
-      <c r="J17" s="137"/>
-      <c r="K17" s="137"/>
-      <c r="L17" s="137"/>
-      <c r="M17" s="121"/>
-    </row>
-    <row r="18" spans="1:13" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="73"/>
-      <c r="B18" s="70"/>
-      <c r="C18" s="70"/>
-      <c r="D18" s="70"/>
-      <c r="E18" s="70"/>
-      <c r="F18" s="70"/>
-      <c r="G18" s="70"/>
-      <c r="H18" s="70"/>
-      <c r="I18" s="70"/>
-      <c r="J18" s="70"/>
-      <c r="K18" s="70"/>
-      <c r="L18" s="70"/>
-      <c r="M18" s="71"/>
-    </row>
-    <row r="19" spans="1:13" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="73"/>
-      <c r="B19" s="91" t="s">
+      <c r="I17" s="91"/>
+      <c r="J17" s="91"/>
+      <c r="K17" s="91"/>
+      <c r="L17" s="91"/>
+      <c r="M17" s="92"/>
+    </row>
+    <row r="18" spans="1:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="148"/>
+      <c r="B18" s="48"/>
+      <c r="C18" s="48"/>
+      <c r="D18" s="48"/>
+      <c r="E18" s="48"/>
+      <c r="F18" s="48"/>
+      <c r="G18" s="48"/>
+      <c r="H18" s="48"/>
+      <c r="I18" s="48"/>
+      <c r="J18" s="48"/>
+      <c r="K18" s="48"/>
+      <c r="L18" s="48"/>
+      <c r="M18" s="49"/>
+    </row>
+    <row r="19" spans="1:13" ht="13.4" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="148"/>
+      <c r="B19" s="96" t="s">
         <v>11</v>
       </c>
-      <c r="C19" s="91"/>
-      <c r="D19" s="147" t="s">
+      <c r="C19" s="96"/>
+      <c r="D19" s="83" t="s">
         <v>12</v>
       </c>
-      <c r="E19" s="148"/>
-      <c r="F19" s="149"/>
-      <c r="G19" s="147" t="s">
+      <c r="E19" s="84"/>
+      <c r="F19" s="85"/>
+      <c r="G19" s="83" t="s">
         <v>13</v>
       </c>
-      <c r="H19" s="148"/>
-      <c r="I19" s="148"/>
-      <c r="J19" s="149"/>
+      <c r="H19" s="84"/>
+      <c r="I19" s="84"/>
+      <c r="J19" s="85"/>
       <c r="K19" s="34"/>
       <c r="L19" s="34"/>
       <c r="M19" s="1"/>
     </row>
-    <row r="20" spans="1:13" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="73"/>
-      <c r="B20" s="91"/>
-      <c r="C20" s="91"/>
-      <c r="D20" s="150"/>
-      <c r="E20" s="151"/>
-      <c r="F20" s="152"/>
-      <c r="G20" s="150"/>
-      <c r="H20" s="151"/>
-      <c r="I20" s="151"/>
-      <c r="J20" s="152"/>
+    <row r="20" spans="1:13" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="148"/>
+      <c r="B20" s="96"/>
+      <c r="C20" s="96"/>
+      <c r="D20" s="86"/>
+      <c r="E20" s="87"/>
+      <c r="F20" s="88"/>
+      <c r="G20" s="86"/>
+      <c r="H20" s="87"/>
+      <c r="I20" s="87"/>
+      <c r="J20" s="88"/>
       <c r="K20" s="34"/>
       <c r="L20" s="34"/>
       <c r="M20" s="1"/>
     </row>
-    <row r="21" spans="1:13" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="73"/>
-      <c r="B21" s="103"/>
-      <c r="C21" s="103"/>
-      <c r="D21" s="103"/>
-      <c r="E21" s="103"/>
-      <c r="F21" s="103"/>
-      <c r="G21" s="103"/>
-      <c r="H21" s="103"/>
-      <c r="I21" s="103"/>
-      <c r="J21" s="103"/>
-      <c r="K21" s="103"/>
-      <c r="L21" s="103"/>
-      <c r="M21" s="104"/>
-    </row>
-    <row r="22" spans="1:13" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="73"/>
-      <c r="B22" s="91" t="s">
+    <row r="21" spans="1:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="148"/>
+      <c r="B21" s="89"/>
+      <c r="C21" s="89"/>
+      <c r="D21" s="89"/>
+      <c r="E21" s="89"/>
+      <c r="F21" s="89"/>
+      <c r="G21" s="89"/>
+      <c r="H21" s="89"/>
+      <c r="I21" s="89"/>
+      <c r="J21" s="89"/>
+      <c r="K21" s="89"/>
+      <c r="L21" s="89"/>
+      <c r="M21" s="90"/>
+    </row>
+    <row r="22" spans="1:13" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="148"/>
+      <c r="B22" s="96" t="s">
         <v>14</v>
       </c>
-      <c r="C22" s="91"/>
-      <c r="D22" s="66"/>
-      <c r="E22" s="67"/>
-      <c r="F22" s="67"/>
-      <c r="G22" s="67"/>
-      <c r="H22" s="67"/>
-      <c r="I22" s="67"/>
-      <c r="J22" s="68"/>
+      <c r="C22" s="96"/>
+      <c r="D22" s="62"/>
+      <c r="E22" s="63"/>
+      <c r="F22" s="63"/>
+      <c r="G22" s="63"/>
+      <c r="H22" s="63"/>
+      <c r="I22" s="63"/>
+      <c r="J22" s="64"/>
       <c r="K22" s="18"/>
       <c r="L22" s="18"/>
       <c r="M22" s="1"/>
     </row>
-    <row r="23" spans="1:13" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="73"/>
-      <c r="B23" s="103"/>
-      <c r="C23" s="103"/>
-      <c r="D23" s="103"/>
-      <c r="E23" s="103"/>
-      <c r="F23" s="103"/>
-      <c r="G23" s="103"/>
-      <c r="H23" s="103"/>
-      <c r="I23" s="103"/>
-      <c r="J23" s="103"/>
-      <c r="K23" s="103"/>
-      <c r="L23" s="103"/>
-      <c r="M23" s="104"/>
-    </row>
-    <row r="24" spans="1:13" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="73"/>
-      <c r="B24" s="91" t="s">
+    <row r="23" spans="1:13" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="148"/>
+      <c r="B23" s="89"/>
+      <c r="C23" s="89"/>
+      <c r="D23" s="89"/>
+      <c r="E23" s="89"/>
+      <c r="F23" s="89"/>
+      <c r="G23" s="89"/>
+      <c r="H23" s="89"/>
+      <c r="I23" s="89"/>
+      <c r="J23" s="89"/>
+      <c r="K23" s="89"/>
+      <c r="L23" s="89"/>
+      <c r="M23" s="90"/>
+    </row>
+    <row r="24" spans="1:13" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="148"/>
+      <c r="B24" s="96" t="s">
         <v>15</v>
       </c>
-      <c r="C24" s="91"/>
-      <c r="D24" s="107"/>
-      <c r="E24" s="108"/>
-      <c r="F24" s="108"/>
-      <c r="G24" s="108"/>
-      <c r="H24" s="108"/>
-      <c r="I24" s="108"/>
-      <c r="J24" s="109"/>
+      <c r="C24" s="96"/>
+      <c r="D24" s="172"/>
+      <c r="E24" s="173"/>
+      <c r="F24" s="173"/>
+      <c r="G24" s="173"/>
+      <c r="H24" s="173"/>
+      <c r="I24" s="173"/>
+      <c r="J24" s="174"/>
       <c r="K24" s="35"/>
       <c r="L24" s="35"/>
       <c r="M24" s="1"/>
     </row>
-    <row r="25" spans="1:13" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="73"/>
-      <c r="B25" s="101"/>
-      <c r="C25" s="101"/>
-      <c r="D25" s="101"/>
-      <c r="E25" s="101"/>
-      <c r="F25" s="101"/>
-      <c r="G25" s="101"/>
-      <c r="H25" s="101"/>
-      <c r="I25" s="101"/>
-      <c r="J25" s="101"/>
-      <c r="K25" s="101"/>
-      <c r="L25" s="101"/>
-      <c r="M25" s="102"/>
-    </row>
-    <row r="26" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="73"/>
-      <c r="B26" s="105" t="s">
+    <row r="25" spans="1:13" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="148"/>
+      <c r="B25" s="51"/>
+      <c r="C25" s="51"/>
+      <c r="D25" s="51"/>
+      <c r="E25" s="51"/>
+      <c r="F25" s="51"/>
+      <c r="G25" s="51"/>
+      <c r="H25" s="51"/>
+      <c r="I25" s="51"/>
+      <c r="J25" s="51"/>
+      <c r="K25" s="51"/>
+      <c r="L25" s="51"/>
+      <c r="M25" s="52"/>
+    </row>
+    <row r="26" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="148"/>
+      <c r="B26" s="170" t="s">
         <v>16</v>
       </c>
-      <c r="C26" s="105"/>
-      <c r="D26" s="105"/>
-      <c r="E26" s="105"/>
-      <c r="F26" s="105"/>
-      <c r="G26" s="105"/>
-      <c r="H26" s="105"/>
-      <c r="I26" s="105"/>
-      <c r="J26" s="105"/>
-      <c r="K26" s="105"/>
-      <c r="L26" s="105"/>
-      <c r="M26" s="106"/>
-    </row>
-    <row r="27" spans="1:13" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="73"/>
-      <c r="B27" s="95"/>
-      <c r="C27" s="95"/>
-      <c r="D27" s="95"/>
-      <c r="E27" s="95"/>
-      <c r="F27" s="95"/>
-      <c r="G27" s="95"/>
-      <c r="H27" s="95"/>
-      <c r="I27" s="95"/>
-      <c r="J27" s="95"/>
-      <c r="K27" s="95"/>
-      <c r="L27" s="95"/>
-      <c r="M27" s="96"/>
-    </row>
-    <row r="28" spans="1:13" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="73"/>
+      <c r="C26" s="170"/>
+      <c r="D26" s="170"/>
+      <c r="E26" s="170"/>
+      <c r="F26" s="170"/>
+      <c r="G26" s="170"/>
+      <c r="H26" s="170"/>
+      <c r="I26" s="170"/>
+      <c r="J26" s="170"/>
+      <c r="K26" s="170"/>
+      <c r="L26" s="170"/>
+      <c r="M26" s="171"/>
+    </row>
+    <row r="27" spans="1:13" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="148"/>
+      <c r="B27" s="166"/>
+      <c r="C27" s="166"/>
+      <c r="D27" s="166"/>
+      <c r="E27" s="166"/>
+      <c r="F27" s="166"/>
+      <c r="G27" s="166"/>
+      <c r="H27" s="166"/>
+      <c r="I27" s="166"/>
+      <c r="J27" s="166"/>
+      <c r="K27" s="166"/>
+      <c r="L27" s="166"/>
+      <c r="M27" s="167"/>
+    </row>
+    <row r="28" spans="1:13" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="148"/>
       <c r="B28" s="25" t="s">
         <v>17</v>
       </c>
-      <c r="C28" s="66"/>
-      <c r="D28" s="67"/>
-      <c r="E28" s="67"/>
-      <c r="F28" s="67"/>
-      <c r="G28" s="67"/>
-      <c r="H28" s="67"/>
-      <c r="I28" s="67"/>
-      <c r="J28" s="67"/>
-      <c r="K28" s="68"/>
+      <c r="C28" s="62"/>
+      <c r="D28" s="63"/>
+      <c r="E28" s="63"/>
+      <c r="F28" s="63"/>
+      <c r="G28" s="63"/>
+      <c r="H28" s="63"/>
+      <c r="I28" s="63"/>
+      <c r="J28" s="63"/>
+      <c r="K28" s="64"/>
       <c r="L28" s="18"/>
       <c r="M28" s="1"/>
     </row>
-    <row r="29" spans="1:13" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="73"/>
-      <c r="B29" s="97"/>
-      <c r="C29" s="97"/>
-      <c r="D29" s="97"/>
-      <c r="E29" s="97"/>
-      <c r="F29" s="97"/>
-      <c r="G29" s="97"/>
-      <c r="H29" s="97"/>
-      <c r="I29" s="97"/>
-      <c r="J29" s="97"/>
-      <c r="K29" s="97"/>
-      <c r="L29" s="97"/>
-      <c r="M29" s="98"/>
-    </row>
-    <row r="30" spans="1:13" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="73"/>
+    <row r="29" spans="1:13" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="148"/>
+      <c r="B29" s="42"/>
+      <c r="C29" s="42"/>
+      <c r="D29" s="42"/>
+      <c r="E29" s="42"/>
+      <c r="F29" s="42"/>
+      <c r="G29" s="42"/>
+      <c r="H29" s="42"/>
+      <c r="I29" s="42"/>
+      <c r="J29" s="42"/>
+      <c r="K29" s="42"/>
+      <c r="L29" s="42"/>
+      <c r="M29" s="43"/>
+    </row>
+    <row r="30" spans="1:13" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="148"/>
       <c r="B30" s="25" t="s">
         <v>18</v>
       </c>
-      <c r="C30" s="66"/>
-      <c r="D30" s="67"/>
-      <c r="E30" s="67"/>
-      <c r="F30" s="68"/>
+      <c r="C30" s="62"/>
+      <c r="D30" s="63"/>
+      <c r="E30" s="63"/>
+      <c r="F30" s="64"/>
       <c r="G30" s="17" t="s">
         <v>60</v>
       </c>
-      <c r="H30" s="66"/>
-      <c r="I30" s="67"/>
-      <c r="J30" s="67"/>
-      <c r="K30" s="68"/>
+      <c r="H30" s="62"/>
+      <c r="I30" s="63"/>
+      <c r="J30" s="63"/>
+      <c r="K30" s="64"/>
       <c r="L30" s="18"/>
       <c r="M30" s="1"/>
     </row>
-    <row r="31" spans="1:13" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="73"/>
+    <row r="31" spans="1:13" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="148"/>
       <c r="B31" s="25"/>
       <c r="C31" s="18"/>
       <c r="D31" s="18"/>
@@ -2788,25 +2775,25 @@
       <c r="L31" s="18"/>
       <c r="M31" s="1"/>
     </row>
-    <row r="32" spans="1:13" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="73"/>
+    <row r="32" spans="1:13" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="148"/>
       <c r="B32" s="25" t="s">
         <v>33</v>
       </c>
-      <c r="C32" s="66"/>
-      <c r="D32" s="67"/>
-      <c r="E32" s="67"/>
-      <c r="F32" s="67"/>
-      <c r="G32" s="67"/>
-      <c r="H32" s="67"/>
-      <c r="I32" s="67"/>
-      <c r="J32" s="67"/>
-      <c r="K32" s="68"/>
+      <c r="C32" s="62"/>
+      <c r="D32" s="63"/>
+      <c r="E32" s="63"/>
+      <c r="F32" s="63"/>
+      <c r="G32" s="63"/>
+      <c r="H32" s="63"/>
+      <c r="I32" s="63"/>
+      <c r="J32" s="63"/>
+      <c r="K32" s="64"/>
       <c r="L32" s="18"/>
       <c r="M32" s="1"/>
     </row>
-    <row r="33" spans="1:13" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="73"/>
+    <row r="33" spans="1:13" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="148"/>
       <c r="B33" s="25"/>
       <c r="C33" s="18"/>
       <c r="D33" s="18"/>
@@ -2820,439 +2807,439 @@
       <c r="L33" s="18"/>
       <c r="M33" s="1"/>
     </row>
-    <row r="34" spans="1:13" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="73"/>
-      <c r="B34" s="64" t="s">
+    <row r="34" spans="1:13" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A34" s="148"/>
+      <c r="B34" s="75" t="s">
         <v>38</v>
       </c>
-      <c r="C34" s="64"/>
-      <c r="D34" s="64"/>
-      <c r="E34" s="64"/>
-      <c r="F34" s="64"/>
-      <c r="G34" s="65"/>
+      <c r="C34" s="75"/>
+      <c r="D34" s="75"/>
+      <c r="E34" s="75"/>
+      <c r="F34" s="75"/>
+      <c r="G34" s="76"/>
       <c r="H34" s="14" t="s">
         <v>48</v>
       </c>
-      <c r="I34" s="146" t="s">
+      <c r="I34" s="74" t="s">
         <v>39</v>
       </c>
-      <c r="J34" s="64"/>
-      <c r="K34" s="65"/>
+      <c r="J34" s="75"/>
+      <c r="K34" s="76"/>
       <c r="L34" s="15"/>
       <c r="M34" s="1"/>
     </row>
-    <row r="35" spans="1:13" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="73"/>
+    <row r="35" spans="1:13" ht="18.649999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="148"/>
       <c r="B35" s="26" t="s">
         <v>40</v>
       </c>
-      <c r="C35" s="66"/>
-      <c r="D35" s="67"/>
-      <c r="E35" s="67"/>
-      <c r="F35" s="67"/>
-      <c r="G35" s="68"/>
+      <c r="C35" s="62"/>
+      <c r="D35" s="63"/>
+      <c r="E35" s="63"/>
+      <c r="F35" s="63"/>
+      <c r="G35" s="64"/>
       <c r="H35" s="11"/>
-      <c r="I35" s="38"/>
-      <c r="J35" s="39"/>
-      <c r="K35" s="40"/>
+      <c r="I35" s="77"/>
+      <c r="J35" s="78"/>
+      <c r="K35" s="79"/>
       <c r="L35" s="18"/>
       <c r="M35" s="1"/>
     </row>
-    <row r="36" spans="1:13" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="73"/>
-      <c r="B36" s="64" t="s">
+    <row r="36" spans="1:13" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A36" s="148"/>
+      <c r="B36" s="75" t="s">
         <v>34</v>
       </c>
-      <c r="C36" s="64"/>
-      <c r="D36" s="64"/>
-      <c r="E36" s="64"/>
-      <c r="F36" s="64"/>
-      <c r="G36" s="64"/>
-      <c r="H36" s="65"/>
-      <c r="I36" s="41"/>
-      <c r="J36" s="42"/>
-      <c r="K36" s="43"/>
+      <c r="C36" s="75"/>
+      <c r="D36" s="75"/>
+      <c r="E36" s="75"/>
+      <c r="F36" s="75"/>
+      <c r="G36" s="75"/>
+      <c r="H36" s="76"/>
+      <c r="I36" s="80"/>
+      <c r="J36" s="81"/>
+      <c r="K36" s="82"/>
       <c r="L36" s="18"/>
       <c r="M36" s="1"/>
     </row>
-    <row r="37" spans="1:13" ht="28.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="73"/>
-      <c r="B37" s="97"/>
-      <c r="C37" s="97"/>
-      <c r="D37" s="97"/>
-      <c r="E37" s="97"/>
-      <c r="F37" s="97"/>
-      <c r="G37" s="97"/>
-      <c r="H37" s="97"/>
-      <c r="I37" s="97"/>
-      <c r="J37" s="97"/>
-      <c r="K37" s="97"/>
-      <c r="L37" s="97"/>
+    <row r="37" spans="1:13" ht="28.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="148"/>
+      <c r="B37" s="42"/>
+      <c r="C37" s="42"/>
+      <c r="D37" s="42"/>
+      <c r="E37" s="42"/>
+      <c r="F37" s="42"/>
+      <c r="G37" s="42"/>
+      <c r="H37" s="42"/>
+      <c r="I37" s="42"/>
+      <c r="J37" s="42"/>
+      <c r="K37" s="42"/>
+      <c r="L37" s="42"/>
       <c r="M37" s="1"/>
     </row>
-    <row r="38" spans="1:13" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="73"/>
-      <c r="B38" s="64" t="s">
+    <row r="38" spans="1:13" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A38" s="148"/>
+      <c r="B38" s="75" t="s">
         <v>35</v>
       </c>
-      <c r="C38" s="64"/>
-      <c r="D38" s="64"/>
-      <c r="E38" s="64"/>
-      <c r="F38" s="64"/>
-      <c r="G38" s="65"/>
+      <c r="C38" s="75"/>
+      <c r="D38" s="75"/>
+      <c r="E38" s="75"/>
+      <c r="F38" s="75"/>
+      <c r="G38" s="76"/>
       <c r="H38" s="14" t="s">
         <v>49</v>
       </c>
-      <c r="I38" s="146" t="s">
+      <c r="I38" s="74" t="s">
         <v>39</v>
       </c>
-      <c r="J38" s="64"/>
-      <c r="K38" s="65"/>
+      <c r="J38" s="75"/>
+      <c r="K38" s="76"/>
       <c r="L38" s="15"/>
       <c r="M38" s="1"/>
     </row>
-    <row r="39" spans="1:13" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="73"/>
+    <row r="39" spans="1:13" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="148"/>
       <c r="B39" s="27" t="s">
         <v>57</v>
       </c>
-      <c r="C39" s="66"/>
-      <c r="D39" s="67"/>
-      <c r="E39" s="67"/>
-      <c r="F39" s="67"/>
-      <c r="G39" s="68"/>
+      <c r="C39" s="62"/>
+      <c r="D39" s="63"/>
+      <c r="E39" s="63"/>
+      <c r="F39" s="63"/>
+      <c r="G39" s="64"/>
       <c r="H39" s="11"/>
-      <c r="I39" s="38"/>
-      <c r="J39" s="39"/>
-      <c r="K39" s="40"/>
+      <c r="I39" s="77"/>
+      <c r="J39" s="78"/>
+      <c r="K39" s="79"/>
       <c r="L39" s="18"/>
       <c r="M39" s="1"/>
     </row>
-    <row r="40" spans="1:13" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="73"/>
-      <c r="B40" s="64" t="s">
+    <row r="40" spans="1:13" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A40" s="148"/>
+      <c r="B40" s="75" t="s">
         <v>52</v>
       </c>
-      <c r="C40" s="64"/>
-      <c r="D40" s="64"/>
-      <c r="E40" s="64"/>
-      <c r="F40" s="64"/>
-      <c r="G40" s="64"/>
-      <c r="H40" s="65"/>
-      <c r="I40" s="41"/>
-      <c r="J40" s="42"/>
-      <c r="K40" s="43"/>
+      <c r="C40" s="75"/>
+      <c r="D40" s="75"/>
+      <c r="E40" s="75"/>
+      <c r="F40" s="75"/>
+      <c r="G40" s="75"/>
+      <c r="H40" s="76"/>
+      <c r="I40" s="80"/>
+      <c r="J40" s="81"/>
+      <c r="K40" s="82"/>
       <c r="L40" s="18"/>
       <c r="M40" s="1"/>
     </row>
-    <row r="41" spans="1:13" ht="29.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="73"/>
-      <c r="B41" s="97"/>
-      <c r="C41" s="97"/>
-      <c r="D41" s="97"/>
-      <c r="E41" s="97"/>
-      <c r="F41" s="97"/>
-      <c r="G41" s="97"/>
-      <c r="H41" s="97"/>
-      <c r="I41" s="97"/>
-      <c r="J41" s="97"/>
-      <c r="K41" s="97"/>
-      <c r="L41" s="97"/>
+    <row r="41" spans="1:13" ht="29.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="148"/>
+      <c r="B41" s="42"/>
+      <c r="C41" s="42"/>
+      <c r="D41" s="42"/>
+      <c r="E41" s="42"/>
+      <c r="F41" s="42"/>
+      <c r="G41" s="42"/>
+      <c r="H41" s="42"/>
+      <c r="I41" s="42"/>
+      <c r="J41" s="42"/>
+      <c r="K41" s="42"/>
+      <c r="L41" s="42"/>
       <c r="M41" s="1"/>
     </row>
-    <row r="42" spans="1:13" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="73"/>
-      <c r="B42" s="64" t="s">
+    <row r="42" spans="1:13" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A42" s="148"/>
+      <c r="B42" s="75" t="s">
         <v>36</v>
       </c>
-      <c r="C42" s="64"/>
-      <c r="D42" s="64"/>
-      <c r="E42" s="64"/>
-      <c r="F42" s="64"/>
-      <c r="G42" s="65"/>
+      <c r="C42" s="75"/>
+      <c r="D42" s="75"/>
+      <c r="E42" s="75"/>
+      <c r="F42" s="75"/>
+      <c r="G42" s="76"/>
       <c r="H42" s="14" t="s">
         <v>50</v>
       </c>
-      <c r="I42" s="146" t="s">
+      <c r="I42" s="74" t="s">
         <v>39</v>
       </c>
-      <c r="J42" s="64"/>
-      <c r="K42" s="65"/>
+      <c r="J42" s="75"/>
+      <c r="K42" s="76"/>
       <c r="L42" s="15"/>
       <c r="M42" s="1"/>
     </row>
-    <row r="43" spans="1:13" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="73"/>
+    <row r="43" spans="1:13" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="148"/>
       <c r="B43" s="26" t="s">
         <v>37</v>
       </c>
-      <c r="C43" s="66"/>
-      <c r="D43" s="67"/>
-      <c r="E43" s="67"/>
-      <c r="F43" s="67"/>
-      <c r="G43" s="68"/>
+      <c r="C43" s="62"/>
+      <c r="D43" s="63"/>
+      <c r="E43" s="63"/>
+      <c r="F43" s="63"/>
+      <c r="G43" s="64"/>
       <c r="H43" s="11"/>
-      <c r="I43" s="38"/>
-      <c r="J43" s="39"/>
-      <c r="K43" s="40"/>
+      <c r="I43" s="77"/>
+      <c r="J43" s="78"/>
+      <c r="K43" s="79"/>
       <c r="L43" s="18"/>
       <c r="M43" s="1"/>
     </row>
-    <row r="44" spans="1:13" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="73"/>
+    <row r="44" spans="1:13" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A44" s="148"/>
       <c r="B44" s="26" t="s">
         <v>55</v>
       </c>
-      <c r="C44" s="66"/>
-      <c r="D44" s="67"/>
-      <c r="E44" s="67"/>
-      <c r="F44" s="67"/>
-      <c r="G44" s="68"/>
+      <c r="C44" s="62"/>
+      <c r="D44" s="63"/>
+      <c r="E44" s="63"/>
+      <c r="F44" s="63"/>
+      <c r="G44" s="64"/>
       <c r="H44" s="16"/>
-      <c r="I44" s="38"/>
-      <c r="J44" s="39"/>
-      <c r="K44" s="40"/>
+      <c r="I44" s="77"/>
+      <c r="J44" s="78"/>
+      <c r="K44" s="79"/>
       <c r="L44" s="18"/>
       <c r="M44" s="1"/>
     </row>
-    <row r="45" spans="1:13" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="73"/>
+    <row r="45" spans="1:13" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A45" s="148"/>
       <c r="B45" s="26" t="s">
         <v>56</v>
       </c>
-      <c r="C45" s="66"/>
-      <c r="D45" s="67"/>
-      <c r="E45" s="67"/>
-      <c r="F45" s="67"/>
-      <c r="G45" s="67"/>
+      <c r="C45" s="62"/>
+      <c r="D45" s="63"/>
+      <c r="E45" s="63"/>
+      <c r="F45" s="63"/>
+      <c r="G45" s="63"/>
       <c r="H45" s="16"/>
-      <c r="I45" s="38"/>
-      <c r="J45" s="39"/>
-      <c r="K45" s="40"/>
+      <c r="I45" s="77"/>
+      <c r="J45" s="78"/>
+      <c r="K45" s="79"/>
       <c r="L45" s="18"/>
       <c r="M45" s="1"/>
     </row>
-    <row r="46" spans="1:13" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="73"/>
-      <c r="B46" s="64" t="s">
+    <row r="46" spans="1:13" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A46" s="148"/>
+      <c r="B46" s="75" t="s">
         <v>51</v>
       </c>
-      <c r="C46" s="64"/>
-      <c r="D46" s="64"/>
-      <c r="E46" s="64"/>
-      <c r="F46" s="64"/>
-      <c r="G46" s="64"/>
-      <c r="H46" s="65"/>
-      <c r="I46" s="41"/>
-      <c r="J46" s="42"/>
-      <c r="K46" s="43"/>
+      <c r="C46" s="75"/>
+      <c r="D46" s="75"/>
+      <c r="E46" s="75"/>
+      <c r="F46" s="75"/>
+      <c r="G46" s="75"/>
+      <c r="H46" s="76"/>
+      <c r="I46" s="80"/>
+      <c r="J46" s="81"/>
+      <c r="K46" s="82"/>
       <c r="L46" s="18"/>
       <c r="M46" s="1"/>
     </row>
-    <row r="47" spans="1:13" ht="33.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="73"/>
-      <c r="B47" s="97"/>
-      <c r="C47" s="97"/>
-      <c r="D47" s="97"/>
-      <c r="E47" s="97"/>
-      <c r="F47" s="97"/>
-      <c r="G47" s="97"/>
-      <c r="H47" s="97"/>
-      <c r="I47" s="97"/>
-      <c r="J47" s="97"/>
-      <c r="K47" s="97"/>
-      <c r="L47" s="97"/>
+    <row r="47" spans="1:13" ht="33.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="148"/>
+      <c r="B47" s="42"/>
+      <c r="C47" s="42"/>
+      <c r="D47" s="42"/>
+      <c r="E47" s="42"/>
+      <c r="F47" s="42"/>
+      <c r="G47" s="42"/>
+      <c r="H47" s="42"/>
+      <c r="I47" s="42"/>
+      <c r="J47" s="42"/>
+      <c r="K47" s="42"/>
+      <c r="L47" s="42"/>
       <c r="M47" s="1"/>
     </row>
-    <row r="48" spans="1:13" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="73"/>
-      <c r="B48" s="47" t="s">
+    <row r="48" spans="1:13" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A48" s="148"/>
+      <c r="B48" s="66" t="s">
         <v>41</v>
       </c>
-      <c r="C48" s="47"/>
-      <c r="D48" s="47"/>
-      <c r="E48" s="47"/>
-      <c r="F48" s="47"/>
-      <c r="G48" s="47"/>
-      <c r="H48" s="47"/>
-      <c r="I48" s="171" t="s">
+      <c r="C48" s="66"/>
+      <c r="D48" s="66"/>
+      <c r="E48" s="66"/>
+      <c r="F48" s="66"/>
+      <c r="G48" s="66"/>
+      <c r="H48" s="66"/>
+      <c r="I48" s="65" t="s">
         <v>39</v>
       </c>
-      <c r="J48" s="47"/>
-      <c r="K48" s="48"/>
+      <c r="J48" s="66"/>
+      <c r="K48" s="67"/>
       <c r="L48" s="36"/>
       <c r="M48" s="1"/>
     </row>
-    <row r="49" spans="1:13" ht="53.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="73"/>
+    <row r="49" spans="1:13" ht="53.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A49" s="148"/>
       <c r="B49" s="20" t="s">
         <v>42</v>
       </c>
-      <c r="C49" s="44"/>
-      <c r="D49" s="45"/>
-      <c r="E49" s="45"/>
-      <c r="F49" s="45"/>
-      <c r="G49" s="45"/>
-      <c r="H49" s="46"/>
-      <c r="I49" s="49"/>
-      <c r="J49" s="50"/>
-      <c r="K49" s="51"/>
+      <c r="C49" s="178"/>
+      <c r="D49" s="179"/>
+      <c r="E49" s="179"/>
+      <c r="F49" s="179"/>
+      <c r="G49" s="179"/>
+      <c r="H49" s="180"/>
+      <c r="I49" s="68"/>
+      <c r="J49" s="69"/>
+      <c r="K49" s="70"/>
       <c r="L49" s="12"/>
       <c r="M49" s="1"/>
     </row>
-    <row r="50" spans="1:13" ht="42.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="73"/>
+    <row r="50" spans="1:13" ht="42.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A50" s="148"/>
       <c r="B50" s="20" t="s">
         <v>43</v>
       </c>
-      <c r="C50" s="52"/>
-      <c r="D50" s="53"/>
-      <c r="E50" s="53"/>
-      <c r="F50" s="53"/>
-      <c r="G50" s="53"/>
-      <c r="H50" s="54"/>
-      <c r="I50" s="49"/>
-      <c r="J50" s="50"/>
-      <c r="K50" s="51"/>
+      <c r="C50" s="181"/>
+      <c r="D50" s="182"/>
+      <c r="E50" s="182"/>
+      <c r="F50" s="182"/>
+      <c r="G50" s="182"/>
+      <c r="H50" s="183"/>
+      <c r="I50" s="68"/>
+      <c r="J50" s="69"/>
+      <c r="K50" s="70"/>
       <c r="L50" s="12"/>
       <c r="M50" s="1"/>
     </row>
-    <row r="51" spans="1:13" ht="45.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="73"/>
+    <row r="51" spans="1:13" ht="45.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A51" s="148"/>
       <c r="B51" s="37" t="s">
         <v>44</v>
       </c>
-      <c r="C51" s="52"/>
-      <c r="D51" s="53"/>
-      <c r="E51" s="53"/>
-      <c r="F51" s="53"/>
-      <c r="G51" s="53"/>
-      <c r="H51" s="54"/>
-      <c r="I51" s="49"/>
-      <c r="J51" s="50"/>
-      <c r="K51" s="51"/>
+      <c r="C51" s="181"/>
+      <c r="D51" s="182"/>
+      <c r="E51" s="182"/>
+      <c r="F51" s="182"/>
+      <c r="G51" s="182"/>
+      <c r="H51" s="183"/>
+      <c r="I51" s="68"/>
+      <c r="J51" s="69"/>
+      <c r="K51" s="70"/>
       <c r="L51" s="12"/>
       <c r="M51" s="1"/>
     </row>
-    <row r="52" spans="1:13" ht="34.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="73"/>
+    <row r="52" spans="1:13" ht="34.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A52" s="148"/>
       <c r="B52" s="20" t="s">
         <v>45</v>
       </c>
-      <c r="C52" s="55"/>
-      <c r="D52" s="56"/>
-      <c r="E52" s="56"/>
-      <c r="F52" s="56"/>
-      <c r="G52" s="56"/>
-      <c r="H52" s="57"/>
-      <c r="I52" s="49"/>
-      <c r="J52" s="50"/>
-      <c r="K52" s="51"/>
+      <c r="C52" s="184"/>
+      <c r="D52" s="185"/>
+      <c r="E52" s="185"/>
+      <c r="F52" s="185"/>
+      <c r="G52" s="185"/>
+      <c r="H52" s="186"/>
+      <c r="I52" s="68"/>
+      <c r="J52" s="69"/>
+      <c r="K52" s="70"/>
       <c r="L52" s="12"/>
       <c r="M52" s="1"/>
     </row>
-    <row r="53" spans="1:13" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="73"/>
+    <row r="53" spans="1:13" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A53" s="148"/>
       <c r="B53" s="20" t="s">
         <v>46</v>
       </c>
-      <c r="C53" s="44"/>
-      <c r="D53" s="45"/>
-      <c r="E53" s="45"/>
-      <c r="F53" s="45"/>
-      <c r="G53" s="45"/>
-      <c r="H53" s="46"/>
-      <c r="I53" s="49"/>
-      <c r="J53" s="50"/>
-      <c r="K53" s="51"/>
+      <c r="C53" s="178"/>
+      <c r="D53" s="179"/>
+      <c r="E53" s="179"/>
+      <c r="F53" s="179"/>
+      <c r="G53" s="179"/>
+      <c r="H53" s="180"/>
+      <c r="I53" s="68"/>
+      <c r="J53" s="69"/>
+      <c r="K53" s="70"/>
       <c r="L53" s="12"/>
       <c r="M53" s="1"/>
     </row>
-    <row r="54" spans="1:13" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="73"/>
-      <c r="B54" s="47" t="s">
+    <row r="54" spans="1:13" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A54" s="148"/>
+      <c r="B54" s="66" t="s">
         <v>47</v>
       </c>
-      <c r="C54" s="47"/>
-      <c r="D54" s="47"/>
-      <c r="E54" s="47"/>
-      <c r="F54" s="47"/>
-      <c r="G54" s="47"/>
-      <c r="H54" s="48"/>
-      <c r="I54" s="172"/>
-      <c r="J54" s="173"/>
-      <c r="K54" s="174"/>
+      <c r="C54" s="66"/>
+      <c r="D54" s="66"/>
+      <c r="E54" s="66"/>
+      <c r="F54" s="66"/>
+      <c r="G54" s="66"/>
+      <c r="H54" s="67"/>
+      <c r="I54" s="71"/>
+      <c r="J54" s="72"/>
+      <c r="K54" s="73"/>
       <c r="L54" s="13"/>
       <c r="M54" s="1"/>
     </row>
-    <row r="55" spans="1:13" ht="39.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="73"/>
-      <c r="B55" s="97"/>
-      <c r="C55" s="97"/>
-      <c r="D55" s="97"/>
-      <c r="E55" s="97"/>
-      <c r="F55" s="97"/>
-      <c r="G55" s="97"/>
-      <c r="H55" s="97"/>
-      <c r="I55" s="97"/>
-      <c r="J55" s="97"/>
-      <c r="K55" s="97"/>
-      <c r="L55" s="97"/>
-      <c r="M55" s="98"/>
-    </row>
-    <row r="56" spans="1:13" ht="46.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="73"/>
-      <c r="B56" s="144" t="s">
+    <row r="55" spans="1:13" ht="39.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A55" s="148"/>
+      <c r="B55" s="42"/>
+      <c r="C55" s="42"/>
+      <c r="D55" s="42"/>
+      <c r="E55" s="42"/>
+      <c r="F55" s="42"/>
+      <c r="G55" s="42"/>
+      <c r="H55" s="42"/>
+      <c r="I55" s="42"/>
+      <c r="J55" s="42"/>
+      <c r="K55" s="42"/>
+      <c r="L55" s="42"/>
+      <c r="M55" s="43"/>
+    </row>
+    <row r="56" spans="1:13" ht="46.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A56" s="148"/>
+      <c r="B56" s="100" t="s">
         <v>58</v>
       </c>
-      <c r="C56" s="145"/>
-      <c r="D56" s="165" t="s">
+      <c r="C56" s="101"/>
+      <c r="D56" s="56" t="s">
         <v>19</v>
       </c>
-      <c r="E56" s="166"/>
-      <c r="F56" s="166"/>
-      <c r="G56" s="166"/>
-      <c r="H56" s="166"/>
-      <c r="I56" s="166"/>
-      <c r="J56" s="166"/>
-      <c r="K56" s="167"/>
+      <c r="E56" s="57"/>
+      <c r="F56" s="57"/>
+      <c r="G56" s="57"/>
+      <c r="H56" s="57"/>
+      <c r="I56" s="57"/>
+      <c r="J56" s="57"/>
+      <c r="K56" s="58"/>
       <c r="L56" s="21"/>
       <c r="M56" s="22"/>
     </row>
-    <row r="57" spans="1:13" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="73"/>
-      <c r="B57" s="99"/>
-      <c r="C57" s="99"/>
-      <c r="D57" s="99"/>
-      <c r="E57" s="99"/>
-      <c r="F57" s="99"/>
-      <c r="G57" s="99"/>
-      <c r="H57" s="99"/>
-      <c r="I57" s="99"/>
-      <c r="J57" s="99"/>
-      <c r="K57" s="99"/>
-      <c r="L57" s="99"/>
-      <c r="M57" s="100"/>
-    </row>
-    <row r="58" spans="1:13" ht="47.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="73"/>
-      <c r="B58" s="144" t="s">
+    <row r="57" spans="1:13" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A57" s="148"/>
+      <c r="B57" s="168"/>
+      <c r="C57" s="168"/>
+      <c r="D57" s="168"/>
+      <c r="E57" s="168"/>
+      <c r="F57" s="168"/>
+      <c r="G57" s="168"/>
+      <c r="H57" s="168"/>
+      <c r="I57" s="168"/>
+      <c r="J57" s="168"/>
+      <c r="K57" s="168"/>
+      <c r="L57" s="168"/>
+      <c r="M57" s="169"/>
+    </row>
+    <row r="58" spans="1:13" ht="47.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A58" s="148"/>
+      <c r="B58" s="100" t="s">
         <v>59</v>
       </c>
-      <c r="C58" s="145"/>
-      <c r="D58" s="168"/>
-      <c r="E58" s="169"/>
-      <c r="F58" s="169"/>
-      <c r="G58" s="169"/>
-      <c r="H58" s="169"/>
-      <c r="I58" s="169"/>
-      <c r="J58" s="169"/>
-      <c r="K58" s="170"/>
+      <c r="C58" s="101"/>
+      <c r="D58" s="59"/>
+      <c r="E58" s="60"/>
+      <c r="F58" s="60"/>
+      <c r="G58" s="60"/>
+      <c r="H58" s="60"/>
+      <c r="I58" s="60"/>
+      <c r="J58" s="60"/>
+      <c r="K58" s="61"/>
       <c r="L58" s="23"/>
       <c r="M58" s="7"/>
     </row>
-    <row r="59" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A59" s="73"/>
+    <row r="59" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A59" s="148"/>
       <c r="B59" s="19"/>
       <c r="C59" s="19"/>
       <c r="D59" s="19"/>
@@ -3266,8 +3253,8 @@
       <c r="L59" s="19"/>
       <c r="M59" s="7"/>
     </row>
-    <row r="60" spans="1:13" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="73"/>
+    <row r="60" spans="1:13" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A60" s="148"/>
       <c r="B60" s="19"/>
       <c r="C60" s="19"/>
       <c r="D60" s="19"/>
@@ -3281,178 +3268,178 @@
       <c r="L60" s="19"/>
       <c r="M60" s="7"/>
     </row>
-    <row r="61" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A61" s="73"/>
-      <c r="B61" s="81" t="s">
+    <row r="61" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A61" s="148"/>
+      <c r="B61" s="99" t="s">
         <v>20</v>
       </c>
-      <c r="C61" s="69"/>
-      <c r="D61" s="70"/>
-      <c r="E61" s="70"/>
-      <c r="F61" s="70"/>
-      <c r="G61" s="70"/>
-      <c r="H61" s="71"/>
-      <c r="I61" s="156" t="s">
+      <c r="C61" s="47"/>
+      <c r="D61" s="48"/>
+      <c r="E61" s="48"/>
+      <c r="F61" s="48"/>
+      <c r="G61" s="48"/>
+      <c r="H61" s="49"/>
+      <c r="I61" s="38" t="s">
         <v>53</v>
       </c>
-      <c r="J61" s="157"/>
-      <c r="K61" s="158"/>
+      <c r="J61" s="39"/>
+      <c r="K61" s="40"/>
       <c r="L61" s="29"/>
       <c r="M61" s="30"/>
     </row>
-    <row r="62" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A62" s="73"/>
-      <c r="B62" s="81"/>
-      <c r="C62" s="163"/>
-      <c r="D62" s="101"/>
-      <c r="E62" s="101"/>
-      <c r="F62" s="101"/>
-      <c r="G62" s="101"/>
-      <c r="H62" s="102"/>
-      <c r="I62" s="159"/>
-      <c r="J62" s="97"/>
-      <c r="K62" s="98"/>
+    <row r="62" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A62" s="148"/>
+      <c r="B62" s="99"/>
+      <c r="C62" s="50"/>
+      <c r="D62" s="51"/>
+      <c r="E62" s="51"/>
+      <c r="F62" s="51"/>
+      <c r="G62" s="51"/>
+      <c r="H62" s="52"/>
+      <c r="I62" s="41"/>
+      <c r="J62" s="42"/>
+      <c r="K62" s="43"/>
       <c r="L62" s="29"/>
       <c r="M62" s="30"/>
     </row>
-    <row r="63" spans="1:13" ht="64.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A63" s="73"/>
-      <c r="B63" s="81"/>
-      <c r="C63" s="164"/>
-      <c r="D63" s="82"/>
-      <c r="E63" s="82"/>
-      <c r="F63" s="82"/>
-      <c r="G63" s="82"/>
-      <c r="H63" s="83"/>
-      <c r="I63" s="160"/>
-      <c r="J63" s="161"/>
-      <c r="K63" s="162"/>
+    <row r="63" spans="1:13" ht="64.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A63" s="148"/>
+      <c r="B63" s="99"/>
+      <c r="C63" s="53"/>
+      <c r="D63" s="54"/>
+      <c r="E63" s="54"/>
+      <c r="F63" s="54"/>
+      <c r="G63" s="54"/>
+      <c r="H63" s="55"/>
+      <c r="I63" s="44"/>
+      <c r="J63" s="45"/>
+      <c r="K63" s="46"/>
       <c r="L63" s="29"/>
       <c r="M63" s="30"/>
     </row>
-    <row r="64" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A64" s="73"/>
-      <c r="B64" s="91"/>
-      <c r="C64" s="91"/>
-      <c r="D64" s="91"/>
-      <c r="E64" s="91"/>
-      <c r="F64" s="91"/>
-      <c r="G64" s="91"/>
-      <c r="H64" s="91"/>
-      <c r="I64" s="91"/>
-      <c r="J64" s="91"/>
-      <c r="K64" s="91"/>
-      <c r="L64" s="91"/>
-      <c r="M64" s="81"/>
-    </row>
-    <row r="65" spans="1:13" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A65" s="73"/>
-      <c r="B65" s="82"/>
-      <c r="C65" s="82"/>
-      <c r="D65" s="82"/>
-      <c r="E65" s="82"/>
-      <c r="F65" s="82"/>
-      <c r="G65" s="82"/>
-      <c r="H65" s="82"/>
-      <c r="I65" s="82"/>
-      <c r="J65" s="82"/>
-      <c r="K65" s="82"/>
-      <c r="L65" s="82"/>
-      <c r="M65" s="83"/>
-    </row>
-    <row r="66" spans="1:13" ht="25.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A66" s="73"/>
-      <c r="B66" s="142" t="s">
+    <row r="64" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A64" s="148"/>
+      <c r="B64" s="96"/>
+      <c r="C64" s="96"/>
+      <c r="D64" s="96"/>
+      <c r="E64" s="96"/>
+      <c r="F64" s="96"/>
+      <c r="G64" s="96"/>
+      <c r="H64" s="96"/>
+      <c r="I64" s="96"/>
+      <c r="J64" s="96"/>
+      <c r="K64" s="96"/>
+      <c r="L64" s="96"/>
+      <c r="M64" s="99"/>
+    </row>
+    <row r="65" spans="1:13" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A65" s="148"/>
+      <c r="B65" s="54"/>
+      <c r="C65" s="54"/>
+      <c r="D65" s="54"/>
+      <c r="E65" s="54"/>
+      <c r="F65" s="54"/>
+      <c r="G65" s="54"/>
+      <c r="H65" s="54"/>
+      <c r="I65" s="54"/>
+      <c r="J65" s="54"/>
+      <c r="K65" s="54"/>
+      <c r="L65" s="54"/>
+      <c r="M65" s="55"/>
+    </row>
+    <row r="66" spans="1:13" ht="25.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A66" s="148"/>
+      <c r="B66" s="97" t="s">
         <v>21</v>
       </c>
-      <c r="C66" s="142"/>
-      <c r="D66" s="142"/>
-      <c r="E66" s="142"/>
-      <c r="F66" s="142"/>
-      <c r="G66" s="142"/>
-      <c r="H66" s="142"/>
-      <c r="I66" s="142"/>
-      <c r="J66" s="142"/>
-      <c r="K66" s="142"/>
-      <c r="L66" s="142"/>
-      <c r="M66" s="143"/>
-    </row>
-    <row r="67" spans="1:13" ht="30.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A67" s="73"/>
-      <c r="B67" s="84" t="s">
+      <c r="C66" s="97"/>
+      <c r="D66" s="97"/>
+      <c r="E66" s="97"/>
+      <c r="F66" s="97"/>
+      <c r="G66" s="97"/>
+      <c r="H66" s="97"/>
+      <c r="I66" s="97"/>
+      <c r="J66" s="97"/>
+      <c r="K66" s="97"/>
+      <c r="L66" s="97"/>
+      <c r="M66" s="98"/>
+    </row>
+    <row r="67" spans="1:13" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A67" s="148"/>
+      <c r="B67" s="156" t="s">
         <v>22</v>
       </c>
-      <c r="C67" s="85"/>
-      <c r="D67" s="88"/>
-      <c r="E67" s="84"/>
-      <c r="F67" s="84"/>
-      <c r="G67" s="84"/>
-      <c r="H67" s="84"/>
-      <c r="I67" s="84"/>
-      <c r="J67" s="84"/>
-      <c r="K67" s="84"/>
-      <c r="L67" s="84"/>
-      <c r="M67" s="89"/>
-    </row>
-    <row r="68" spans="1:13" ht="30.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A68" s="73"/>
-      <c r="B68" s="86"/>
-      <c r="C68" s="86"/>
-      <c r="D68" s="90"/>
-      <c r="E68" s="91"/>
-      <c r="F68" s="91"/>
-      <c r="G68" s="91"/>
-      <c r="H68" s="91"/>
-      <c r="I68" s="91"/>
-      <c r="J68" s="91"/>
-      <c r="K68" s="91"/>
-      <c r="L68" s="91"/>
-      <c r="M68" s="81"/>
-    </row>
-    <row r="69" spans="1:13" ht="30.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A69" s="73"/>
-      <c r="B69" s="86"/>
-      <c r="C69" s="86"/>
-      <c r="D69" s="90"/>
-      <c r="E69" s="91"/>
-      <c r="F69" s="91"/>
-      <c r="G69" s="91"/>
-      <c r="H69" s="91"/>
-      <c r="I69" s="91"/>
-      <c r="J69" s="91"/>
-      <c r="K69" s="91"/>
-      <c r="L69" s="91"/>
-      <c r="M69" s="81"/>
-    </row>
-    <row r="70" spans="1:13" ht="30.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A70" s="73"/>
-      <c r="B70" s="86"/>
-      <c r="C70" s="86"/>
-      <c r="D70" s="90"/>
-      <c r="E70" s="91"/>
-      <c r="F70" s="91"/>
-      <c r="G70" s="91"/>
-      <c r="H70" s="91"/>
-      <c r="I70" s="91"/>
-      <c r="J70" s="91"/>
-      <c r="K70" s="91"/>
-      <c r="L70" s="91"/>
-      <c r="M70" s="81"/>
-    </row>
-    <row r="71" spans="1:13" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A71" s="74"/>
-      <c r="B71" s="87"/>
-      <c r="C71" s="87"/>
-      <c r="D71" s="92"/>
-      <c r="E71" s="93"/>
-      <c r="F71" s="93"/>
-      <c r="G71" s="93"/>
-      <c r="H71" s="93"/>
-      <c r="I71" s="93"/>
-      <c r="J71" s="93"/>
-      <c r="K71" s="93"/>
-      <c r="L71" s="93"/>
-      <c r="M71" s="94"/>
+      <c r="C67" s="157"/>
+      <c r="D67" s="160"/>
+      <c r="E67" s="156"/>
+      <c r="F67" s="156"/>
+      <c r="G67" s="156"/>
+      <c r="H67" s="156"/>
+      <c r="I67" s="156"/>
+      <c r="J67" s="156"/>
+      <c r="K67" s="156"/>
+      <c r="L67" s="156"/>
+      <c r="M67" s="161"/>
+    </row>
+    <row r="68" spans="1:13" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A68" s="148"/>
+      <c r="B68" s="158"/>
+      <c r="C68" s="158"/>
+      <c r="D68" s="162"/>
+      <c r="E68" s="96"/>
+      <c r="F68" s="96"/>
+      <c r="G68" s="96"/>
+      <c r="H68" s="96"/>
+      <c r="I68" s="96"/>
+      <c r="J68" s="96"/>
+      <c r="K68" s="96"/>
+      <c r="L68" s="96"/>
+      <c r="M68" s="99"/>
+    </row>
+    <row r="69" spans="1:13" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A69" s="148"/>
+      <c r="B69" s="158"/>
+      <c r="C69" s="158"/>
+      <c r="D69" s="162"/>
+      <c r="E69" s="96"/>
+      <c r="F69" s="96"/>
+      <c r="G69" s="96"/>
+      <c r="H69" s="96"/>
+      <c r="I69" s="96"/>
+      <c r="J69" s="96"/>
+      <c r="K69" s="96"/>
+      <c r="L69" s="96"/>
+      <c r="M69" s="99"/>
+    </row>
+    <row r="70" spans="1:13" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A70" s="148"/>
+      <c r="B70" s="158"/>
+      <c r="C70" s="158"/>
+      <c r="D70" s="162"/>
+      <c r="E70" s="96"/>
+      <c r="F70" s="96"/>
+      <c r="G70" s="96"/>
+      <c r="H70" s="96"/>
+      <c r="I70" s="96"/>
+      <c r="J70" s="96"/>
+      <c r="K70" s="96"/>
+      <c r="L70" s="96"/>
+      <c r="M70" s="99"/>
+    </row>
+    <row r="71" spans="1:13" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A71" s="149"/>
+      <c r="B71" s="159"/>
+      <c r="C71" s="159"/>
+      <c r="D71" s="163"/>
+      <c r="E71" s="164"/>
+      <c r="F71" s="164"/>
+      <c r="G71" s="164"/>
+      <c r="H71" s="164"/>
+      <c r="I71" s="164"/>
+      <c r="J71" s="164"/>
+      <c r="K71" s="164"/>
+      <c r="L71" s="164"/>
+      <c r="M71" s="165"/>
     </row>
   </sheetData>
   <sheetProtection formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0" pivotTables="0"/>
@@ -3460,6 +3447,86 @@
     <protectedRange sqref="C61 C13:C15 D22:D24 E17 G17 J17:L17 D19 C28 D56 D58 I13:I15 C30:C54 G30:G54" name="Rango1"/>
   </protectedRanges>
   <mergeCells count="96">
+    <mergeCell ref="I45:K45"/>
+    <mergeCell ref="I46:K46"/>
+    <mergeCell ref="C53:H53"/>
+    <mergeCell ref="B54:H54"/>
+    <mergeCell ref="I49:K49"/>
+    <mergeCell ref="I50:K50"/>
+    <mergeCell ref="B48:H48"/>
+    <mergeCell ref="C49:H49"/>
+    <mergeCell ref="C50:H50"/>
+    <mergeCell ref="C51:H51"/>
+    <mergeCell ref="C52:H52"/>
+    <mergeCell ref="D6:H7"/>
+    <mergeCell ref="B34:G34"/>
+    <mergeCell ref="C35:G35"/>
+    <mergeCell ref="B36:H36"/>
+    <mergeCell ref="C39:G39"/>
+    <mergeCell ref="B38:G38"/>
+    <mergeCell ref="A1:M1"/>
+    <mergeCell ref="A2:A71"/>
+    <mergeCell ref="B2:C7"/>
+    <mergeCell ref="B61:B63"/>
+    <mergeCell ref="B65:M65"/>
+    <mergeCell ref="B67:C71"/>
+    <mergeCell ref="D67:M71"/>
+    <mergeCell ref="B27:M27"/>
+    <mergeCell ref="B29:M29"/>
+    <mergeCell ref="B55:M55"/>
+    <mergeCell ref="B57:M57"/>
+    <mergeCell ref="B25:M25"/>
+    <mergeCell ref="B23:M23"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="B26:M26"/>
+    <mergeCell ref="D24:J24"/>
+    <mergeCell ref="I2:M3"/>
+    <mergeCell ref="B8:M8"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="B9:M9"/>
+    <mergeCell ref="B11:M11"/>
+    <mergeCell ref="C13:F13"/>
+    <mergeCell ref="G13:H13"/>
+    <mergeCell ref="B12:M12"/>
+    <mergeCell ref="B16:M16"/>
+    <mergeCell ref="B14:F14"/>
+    <mergeCell ref="D2:H3"/>
+    <mergeCell ref="D4:H5"/>
+    <mergeCell ref="H17:M17"/>
+    <mergeCell ref="I4:M5"/>
+    <mergeCell ref="I6:M6"/>
+    <mergeCell ref="I7:M7"/>
+    <mergeCell ref="B66:M66"/>
+    <mergeCell ref="B64:M64"/>
+    <mergeCell ref="B56:C56"/>
+    <mergeCell ref="B58:C58"/>
+    <mergeCell ref="B37:L37"/>
+    <mergeCell ref="B41:L41"/>
+    <mergeCell ref="B47:L47"/>
+    <mergeCell ref="B40:H40"/>
+    <mergeCell ref="I38:K38"/>
+    <mergeCell ref="I39:K39"/>
+    <mergeCell ref="I40:K40"/>
+    <mergeCell ref="C43:G43"/>
+    <mergeCell ref="B42:G42"/>
+    <mergeCell ref="B46:H46"/>
+    <mergeCell ref="C44:G44"/>
+    <mergeCell ref="C45:G45"/>
+    <mergeCell ref="I13:K13"/>
+    <mergeCell ref="I15:K15"/>
+    <mergeCell ref="I34:K34"/>
+    <mergeCell ref="I35:K35"/>
+    <mergeCell ref="I36:K36"/>
+    <mergeCell ref="H14:M14"/>
+    <mergeCell ref="D22:J22"/>
+    <mergeCell ref="D19:F20"/>
+    <mergeCell ref="G19:J20"/>
+    <mergeCell ref="B18:M18"/>
+    <mergeCell ref="B21:M21"/>
+    <mergeCell ref="B17:E17"/>
+    <mergeCell ref="C15:F15"/>
+    <mergeCell ref="B19:C20"/>
+    <mergeCell ref="B22:C22"/>
     <mergeCell ref="I61:K63"/>
     <mergeCell ref="C61:H63"/>
     <mergeCell ref="D56:K56"/>
@@ -3476,90 +3543,10 @@
     <mergeCell ref="I42:K42"/>
     <mergeCell ref="I43:K43"/>
     <mergeCell ref="I44:K44"/>
-    <mergeCell ref="I13:K13"/>
-    <mergeCell ref="I15:K15"/>
-    <mergeCell ref="I34:K34"/>
-    <mergeCell ref="I35:K35"/>
-    <mergeCell ref="I36:K36"/>
-    <mergeCell ref="H14:M14"/>
-    <mergeCell ref="D22:J22"/>
-    <mergeCell ref="D19:F20"/>
-    <mergeCell ref="G19:J20"/>
-    <mergeCell ref="B18:M18"/>
-    <mergeCell ref="B21:M21"/>
-    <mergeCell ref="B17:E17"/>
-    <mergeCell ref="C15:F15"/>
-    <mergeCell ref="B19:C20"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="B66:M66"/>
-    <mergeCell ref="B64:M64"/>
-    <mergeCell ref="B56:C56"/>
-    <mergeCell ref="B58:C58"/>
-    <mergeCell ref="B37:L37"/>
-    <mergeCell ref="B41:L41"/>
-    <mergeCell ref="B47:L47"/>
-    <mergeCell ref="B40:H40"/>
-    <mergeCell ref="I38:K38"/>
-    <mergeCell ref="I39:K39"/>
-    <mergeCell ref="I40:K40"/>
-    <mergeCell ref="C43:G43"/>
-    <mergeCell ref="B42:G42"/>
-    <mergeCell ref="B46:H46"/>
-    <mergeCell ref="C44:G44"/>
-    <mergeCell ref="C45:G45"/>
-    <mergeCell ref="I2:M3"/>
-    <mergeCell ref="B8:M8"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="B9:M9"/>
-    <mergeCell ref="B11:M11"/>
-    <mergeCell ref="C13:F13"/>
-    <mergeCell ref="G13:H13"/>
-    <mergeCell ref="B12:M12"/>
-    <mergeCell ref="B16:M16"/>
-    <mergeCell ref="B14:F14"/>
-    <mergeCell ref="D2:H3"/>
-    <mergeCell ref="D4:H5"/>
-    <mergeCell ref="H17:M17"/>
-    <mergeCell ref="I4:M5"/>
-    <mergeCell ref="I6:M6"/>
-    <mergeCell ref="I7:M7"/>
-    <mergeCell ref="A1:M1"/>
-    <mergeCell ref="A2:A71"/>
-    <mergeCell ref="B2:C7"/>
-    <mergeCell ref="B61:B63"/>
-    <mergeCell ref="B65:M65"/>
-    <mergeCell ref="B67:C71"/>
-    <mergeCell ref="D67:M71"/>
-    <mergeCell ref="B27:M27"/>
-    <mergeCell ref="B29:M29"/>
-    <mergeCell ref="B55:M55"/>
-    <mergeCell ref="B57:M57"/>
-    <mergeCell ref="B25:M25"/>
-    <mergeCell ref="B23:M23"/>
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="B26:M26"/>
-    <mergeCell ref="D24:J24"/>
-    <mergeCell ref="D6:H7"/>
-    <mergeCell ref="B34:G34"/>
-    <mergeCell ref="C35:G35"/>
-    <mergeCell ref="B36:H36"/>
-    <mergeCell ref="C39:G39"/>
-    <mergeCell ref="B38:G38"/>
-    <mergeCell ref="I45:K45"/>
-    <mergeCell ref="I46:K46"/>
-    <mergeCell ref="C53:H53"/>
-    <mergeCell ref="B54:H54"/>
-    <mergeCell ref="I49:K49"/>
-    <mergeCell ref="I50:K50"/>
-    <mergeCell ref="B48:H48"/>
-    <mergeCell ref="C49:H49"/>
-    <mergeCell ref="C50:H50"/>
-    <mergeCell ref="C51:H51"/>
-    <mergeCell ref="C52:H52"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.39370078740157483" right="0.39370078740157483" top="0.39370078740157483" bottom="0.39370078740157483" header="0" footer="0"/>
-  <pageSetup scale="52" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="5" scale="61" orientation="portrait" r:id="rId1"/>
   <headerFooter alignWithMargins="0"/>
   <drawing r:id="rId2"/>
   <legacyDrawing r:id="rId3"/>
@@ -3569,37 +3556,37 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.453125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="8.42578125" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="17.7109375" style="3" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="57.140625" style="3" customWidth="1"/>
-    <col min="4" max="16384" width="11.42578125" style="3"/>
+    <col min="1" max="1" width="8.453125" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.7265625" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="57.1796875" style="3" customWidth="1"/>
+    <col min="4" max="16384" width="11.453125" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="175" t="s">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A1" s="187" t="s">
         <v>23</v>
       </c>
-      <c r="B1" s="177" t="s">
+      <c r="B1" s="189" t="s">
         <v>24</v>
       </c>
-      <c r="C1" s="175" t="s">
+      <c r="C1" s="187" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="176" t="s">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A2" s="188" t="s">
         <v>26</v>
       </c>
-      <c r="B2" s="178">
+      <c r="B2" s="190">
         <v>42397</v>
       </c>
-      <c r="C2" s="176" t="s">
+      <c r="C2" s="188" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="4" t="s">
         <v>26</v>
       </c>
@@ -3610,7 +3597,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" ht="60" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="4" t="s">
         <v>29</v>
       </c>
@@ -3621,7 +3608,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="58.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" ht="58.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="4" t="s">
         <v>31</v>
       </c>
@@ -3632,7 +3619,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="77.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" ht="77.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="4" t="s">
         <v>61</v>
       </c>
